--- a/data/processed/clean_data.xlsx
+++ b/data/processed/clean_data.xlsx
@@ -768,7 +768,7 @@
         <v>35.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P5" t="n">
         <v>1.471314899904323</v>
@@ -832,7 +832,7 @@
         <v>22.5</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2397677075546296</v>
@@ -896,7 +896,7 @@
         <v>30.8</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P7" t="n">
         <v>0.9245290682754905</v>
@@ -960,7 +960,7 @@
         <v>18.6</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P8" t="n">
         <v>-1.185733188093377</v>
@@ -1024,7 +1024,7 @@
         <v>25.5</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P9" t="n">
         <v>-0.6077571714229204</v>
@@ -1408,7 +1408,7 @@
         <v>35.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P15" t="n">
         <v>1.471314899904323</v>
@@ -1472,7 +1472,7 @@
         <v>22.5</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P16" t="n">
         <v>-0.2397677075546296</v>
@@ -1536,7 +1536,7 @@
         <v>30.8</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P17" t="n">
         <v>0.9245290682754905</v>
@@ -1600,7 +1600,7 @@
         <v>18.6</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P18" t="n">
         <v>-1.185733188093377</v>
@@ -1664,7 +1664,7 @@
         <v>25.5</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P19" t="n">
         <v>-0.6077571714229204</v>
@@ -2048,7 +2048,7 @@
         <v>35.2</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P25" t="n">
         <v>1.471314899904323</v>
@@ -2112,7 +2112,7 @@
         <v>22.5</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P26" t="n">
         <v>-0.2397677075546296</v>
@@ -2176,7 +2176,7 @@
         <v>30.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P27" t="n">
         <v>0.9245290682754905</v>
@@ -2240,7 +2240,7 @@
         <v>18.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P28" t="n">
         <v>-1.185733188093377</v>
@@ -2304,7 +2304,7 @@
         <v>25.5</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P29" t="n">
         <v>-0.6077571714229204</v>
@@ -2688,7 +2688,7 @@
         <v>35.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P35" t="n">
         <v>1.471314899904323</v>
@@ -2752,7 +2752,7 @@
         <v>22.5</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P36" t="n">
         <v>-0.2397677075546296</v>
@@ -2816,7 +2816,7 @@
         <v>30.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P37" t="n">
         <v>0.9245290682754905</v>
@@ -2880,7 +2880,7 @@
         <v>18.6</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P38" t="n">
         <v>-1.185733188093377</v>
@@ -2944,7 +2944,7 @@
         <v>25.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P39" t="n">
         <v>-0.6077571714229204</v>
@@ -3328,7 +3328,7 @@
         <v>35.2</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P45" t="n">
         <v>1.471314899904323</v>
@@ -3392,7 +3392,7 @@
         <v>22.5</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P46" t="n">
         <v>-0.2397677075546296</v>
@@ -3456,7 +3456,7 @@
         <v>30.8</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P47" t="n">
         <v>0.9245290682754905</v>
@@ -3520,7 +3520,7 @@
         <v>18.6</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P48" t="n">
         <v>-1.185733188093377</v>
@@ -3584,7 +3584,7 @@
         <v>25.5</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P49" t="n">
         <v>-0.6077571714229204</v>
@@ -3968,7 +3968,7 @@
         <v>35.2</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P55" t="n">
         <v>1.471314899904323</v>
@@ -4032,7 +4032,7 @@
         <v>22.5</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P56" t="n">
         <v>-0.2397677075546296</v>
@@ -4096,7 +4096,7 @@
         <v>30.8</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P57" t="n">
         <v>0.9245290682754905</v>
@@ -4160,7 +4160,7 @@
         <v>18.6</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P58" t="n">
         <v>-1.185733188093377</v>
@@ -4224,7 +4224,7 @@
         <v>25.5</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P59" t="n">
         <v>-0.6077571714229204</v>
@@ -4608,7 +4608,7 @@
         <v>35.2</v>
       </c>
       <c r="O65" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P65" t="n">
         <v>1.471314899904323</v>
@@ -4672,7 +4672,7 @@
         <v>22.5</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P66" t="n">
         <v>-0.2397677075546296</v>
@@ -4736,7 +4736,7 @@
         <v>30.8</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P67" t="n">
         <v>0.9245290682754905</v>
@@ -4800,7 +4800,7 @@
         <v>18.6</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P68" t="n">
         <v>-1.185733188093377</v>
@@ -4864,7 +4864,7 @@
         <v>25.5</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P69" t="n">
         <v>-0.6077571714229204</v>
@@ -5248,7 +5248,7 @@
         <v>35.2</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P75" t="n">
         <v>1.471314899904323</v>
@@ -5312,7 +5312,7 @@
         <v>22.5</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P76" t="n">
         <v>-0.2397677075546296</v>
@@ -5376,7 +5376,7 @@
         <v>30.8</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P77" t="n">
         <v>0.9245290682754905</v>
@@ -5440,7 +5440,7 @@
         <v>18.6</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P78" t="n">
         <v>-1.185733188093377</v>
@@ -5504,7 +5504,7 @@
         <v>25.5</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P79" t="n">
         <v>-0.6077571714229204</v>
@@ -5888,7 +5888,7 @@
         <v>35.2</v>
       </c>
       <c r="O85" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P85" t="n">
         <v>1.471314899904323</v>
@@ -5952,7 +5952,7 @@
         <v>22.5</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P86" t="n">
         <v>-0.2397677075546296</v>
@@ -6016,7 +6016,7 @@
         <v>30.8</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P87" t="n">
         <v>0.9245290682754905</v>
@@ -6080,7 +6080,7 @@
         <v>18.6</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P88" t="n">
         <v>-1.185733188093377</v>
@@ -6144,7 +6144,7 @@
         <v>25.5</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P89" t="n">
         <v>-0.6077571714229204</v>
@@ -6528,7 +6528,7 @@
         <v>35.2</v>
       </c>
       <c r="O95" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P95" t="n">
         <v>1.471314899904323</v>
@@ -6592,7 +6592,7 @@
         <v>22.5</v>
       </c>
       <c r="O96" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P96" t="n">
         <v>-0.2397677075546296</v>
@@ -6656,7 +6656,7 @@
         <v>30.8</v>
       </c>
       <c r="O97" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P97" t="n">
         <v>0.9245290682754905</v>
@@ -6720,7 +6720,7 @@
         <v>18.6</v>
       </c>
       <c r="O98" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P98" t="n">
         <v>-1.185733188093377</v>
@@ -6784,7 +6784,7 @@
         <v>25.5</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P99" t="n">
         <v>-0.6077571714229204</v>
@@ -7168,7 +7168,7 @@
         <v>35.2</v>
       </c>
       <c r="O105" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P105" t="n">
         <v>1.471314899904323</v>
@@ -7232,7 +7232,7 @@
         <v>22.5</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P106" t="n">
         <v>-0.2397677075546296</v>
@@ -7296,7 +7296,7 @@
         <v>30.8</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P107" t="n">
         <v>0.9245290682754905</v>
@@ -7360,7 +7360,7 @@
         <v>18.6</v>
       </c>
       <c r="O108" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P108" t="n">
         <v>-1.185733188093377</v>
@@ -7424,7 +7424,7 @@
         <v>25.5</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P109" t="n">
         <v>-0.6077571714229204</v>
@@ -7808,7 +7808,7 @@
         <v>35.2</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P115" t="n">
         <v>1.471314899904323</v>
@@ -7872,7 +7872,7 @@
         <v>22.5</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P116" t="n">
         <v>-0.2397677075546296</v>
@@ -7936,7 +7936,7 @@
         <v>30.8</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P117" t="n">
         <v>0.9245290682754905</v>
@@ -8000,7 +8000,7 @@
         <v>18.6</v>
       </c>
       <c r="O118" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P118" t="n">
         <v>-1.185733188093377</v>
@@ -8064,7 +8064,7 @@
         <v>25.5</v>
       </c>
       <c r="O119" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P119" t="n">
         <v>-0.6077571714229204</v>
@@ -8448,7 +8448,7 @@
         <v>35.2</v>
       </c>
       <c r="O125" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P125" t="n">
         <v>1.471314899904323</v>
@@ -8512,7 +8512,7 @@
         <v>22.5</v>
       </c>
       <c r="O126" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P126" t="n">
         <v>-0.2397677075546296</v>
@@ -8576,7 +8576,7 @@
         <v>30.8</v>
       </c>
       <c r="O127" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P127" t="n">
         <v>0.9245290682754905</v>
@@ -8640,7 +8640,7 @@
         <v>18.6</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P128" t="n">
         <v>-1.185733188093377</v>
@@ -8704,7 +8704,7 @@
         <v>25.5</v>
       </c>
       <c r="O129" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P129" t="n">
         <v>-0.6077571714229204</v>
@@ -9088,7 +9088,7 @@
         <v>35.2</v>
       </c>
       <c r="O135" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P135" t="n">
         <v>1.471314899904323</v>
@@ -9152,7 +9152,7 @@
         <v>22.5</v>
       </c>
       <c r="O136" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P136" t="n">
         <v>-0.2397677075546296</v>
@@ -9216,7 +9216,7 @@
         <v>30.8</v>
       </c>
       <c r="O137" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P137" t="n">
         <v>0.9245290682754905</v>
@@ -9280,7 +9280,7 @@
         <v>18.6</v>
       </c>
       <c r="O138" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P138" t="n">
         <v>-1.185733188093377</v>
@@ -9344,7 +9344,7 @@
         <v>25.5</v>
       </c>
       <c r="O139" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P139" t="n">
         <v>-0.6077571714229204</v>
@@ -9728,7 +9728,7 @@
         <v>35.2</v>
       </c>
       <c r="O145" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P145" t="n">
         <v>1.471314899904323</v>
@@ -9792,7 +9792,7 @@
         <v>22.5</v>
       </c>
       <c r="O146" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P146" t="n">
         <v>-0.2397677075546296</v>
@@ -9856,7 +9856,7 @@
         <v>30.8</v>
       </c>
       <c r="O147" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P147" t="n">
         <v>0.9245290682754905</v>
@@ -9920,7 +9920,7 @@
         <v>18.6</v>
       </c>
       <c r="O148" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P148" t="n">
         <v>-1.185733188093377</v>
@@ -9984,7 +9984,7 @@
         <v>25.5</v>
       </c>
       <c r="O149" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P149" t="n">
         <v>-0.6077571714229204</v>
@@ -10368,7 +10368,7 @@
         <v>35.2</v>
       </c>
       <c r="O155" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P155" t="n">
         <v>1.471314899904323</v>
@@ -10432,7 +10432,7 @@
         <v>22.5</v>
       </c>
       <c r="O156" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P156" t="n">
         <v>-0.2397677075546296</v>
@@ -10496,7 +10496,7 @@
         <v>30.8</v>
       </c>
       <c r="O157" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P157" t="n">
         <v>0.9245290682754905</v>
@@ -10560,7 +10560,7 @@
         <v>18.6</v>
       </c>
       <c r="O158" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P158" t="n">
         <v>-1.185733188093377</v>
@@ -10624,7 +10624,7 @@
         <v>25.5</v>
       </c>
       <c r="O159" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P159" t="n">
         <v>-0.6077571714229204</v>
@@ -11008,7 +11008,7 @@
         <v>35.2</v>
       </c>
       <c r="O165" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P165" t="n">
         <v>1.471314899904323</v>
@@ -11072,7 +11072,7 @@
         <v>22.5</v>
       </c>
       <c r="O166" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P166" t="n">
         <v>-0.2397677075546296</v>
@@ -11136,7 +11136,7 @@
         <v>30.8</v>
       </c>
       <c r="O167" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P167" t="n">
         <v>0.9245290682754905</v>
@@ -11200,7 +11200,7 @@
         <v>18.6</v>
       </c>
       <c r="O168" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P168" t="n">
         <v>-1.185733188093377</v>
@@ -11264,7 +11264,7 @@
         <v>25.5</v>
       </c>
       <c r="O169" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P169" t="n">
         <v>-0.6077571714229204</v>
@@ -11648,7 +11648,7 @@
         <v>35.2</v>
       </c>
       <c r="O175" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P175" t="n">
         <v>1.471314899904323</v>
@@ -11712,7 +11712,7 @@
         <v>22.5</v>
       </c>
       <c r="O176" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P176" t="n">
         <v>-0.2397677075546296</v>
@@ -11776,7 +11776,7 @@
         <v>30.8</v>
       </c>
       <c r="O177" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P177" t="n">
         <v>0.9245290682754905</v>
@@ -11840,7 +11840,7 @@
         <v>18.6</v>
       </c>
       <c r="O178" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P178" t="n">
         <v>-1.185733188093377</v>
@@ -11904,7 +11904,7 @@
         <v>25.5</v>
       </c>
       <c r="O179" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P179" t="n">
         <v>-0.6077571714229204</v>
@@ -12288,7 +12288,7 @@
         <v>35.2</v>
       </c>
       <c r="O185" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P185" t="n">
         <v>1.471314899904323</v>
@@ -12352,7 +12352,7 @@
         <v>22.5</v>
       </c>
       <c r="O186" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P186" t="n">
         <v>-0.2397677075546296</v>
@@ -12416,7 +12416,7 @@
         <v>30.8</v>
       </c>
       <c r="O187" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P187" t="n">
         <v>0.9245290682754905</v>
@@ -12480,7 +12480,7 @@
         <v>18.6</v>
       </c>
       <c r="O188" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P188" t="n">
         <v>-1.185733188093377</v>
@@ -12544,7 +12544,7 @@
         <v>25.5</v>
       </c>
       <c r="O189" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P189" t="n">
         <v>-0.6077571714229204</v>
@@ -12928,7 +12928,7 @@
         <v>35.2</v>
       </c>
       <c r="O195" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P195" t="n">
         <v>1.471314899904323</v>
@@ -12992,7 +12992,7 @@
         <v>22.5</v>
       </c>
       <c r="O196" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P196" t="n">
         <v>-0.2397677075546296</v>
@@ -13056,7 +13056,7 @@
         <v>30.8</v>
       </c>
       <c r="O197" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P197" t="n">
         <v>0.9245290682754905</v>
@@ -13120,7 +13120,7 @@
         <v>18.6</v>
       </c>
       <c r="O198" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P198" t="n">
         <v>-1.185733188093377</v>
@@ -13184,7 +13184,7 @@
         <v>25.5</v>
       </c>
       <c r="O199" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P199" t="n">
         <v>-0.6077571714229204</v>
@@ -13568,7 +13568,7 @@
         <v>35.2</v>
       </c>
       <c r="O205" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P205" t="n">
         <v>1.471314899904323</v>
@@ -13632,7 +13632,7 @@
         <v>22.5</v>
       </c>
       <c r="O206" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P206" t="n">
         <v>-0.2397677075546296</v>
@@ -13696,7 +13696,7 @@
         <v>30.8</v>
       </c>
       <c r="O207" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P207" t="n">
         <v>0.9245290682754905</v>
@@ -13760,7 +13760,7 @@
         <v>18.6</v>
       </c>
       <c r="O208" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P208" t="n">
         <v>-1.185733188093377</v>
@@ -13824,7 +13824,7 @@
         <v>25.5</v>
       </c>
       <c r="O209" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P209" t="n">
         <v>-0.6077571714229204</v>
@@ -14208,7 +14208,7 @@
         <v>35.2</v>
       </c>
       <c r="O215" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P215" t="n">
         <v>1.471314899904323</v>
@@ -14272,7 +14272,7 @@
         <v>22.5</v>
       </c>
       <c r="O216" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P216" t="n">
         <v>-0.2397677075546296</v>
@@ -14336,7 +14336,7 @@
         <v>30.8</v>
       </c>
       <c r="O217" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P217" t="n">
         <v>0.9245290682754905</v>
@@ -14400,7 +14400,7 @@
         <v>18.6</v>
       </c>
       <c r="O218" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P218" t="n">
         <v>-1.185733188093377</v>
@@ -14464,7 +14464,7 @@
         <v>25.5</v>
       </c>
       <c r="O219" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P219" t="n">
         <v>-0.6077571714229204</v>
@@ -14848,7 +14848,7 @@
         <v>35.2</v>
       </c>
       <c r="O225" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P225" t="n">
         <v>1.471314899904323</v>
@@ -14912,7 +14912,7 @@
         <v>22.5</v>
       </c>
       <c r="O226" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P226" t="n">
         <v>-0.2397677075546296</v>
@@ -14976,7 +14976,7 @@
         <v>30.8</v>
       </c>
       <c r="O227" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P227" t="n">
         <v>0.9245290682754905</v>
@@ -15040,7 +15040,7 @@
         <v>18.6</v>
       </c>
       <c r="O228" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P228" t="n">
         <v>-1.185733188093377</v>
@@ -15104,7 +15104,7 @@
         <v>25.5</v>
       </c>
       <c r="O229" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P229" t="n">
         <v>-0.6077571714229204</v>
@@ -15488,7 +15488,7 @@
         <v>35.2</v>
       </c>
       <c r="O235" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P235" t="n">
         <v>1.471314899904323</v>
@@ -15552,7 +15552,7 @@
         <v>22.5</v>
       </c>
       <c r="O236" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P236" t="n">
         <v>-0.2397677075546296</v>
@@ -15616,7 +15616,7 @@
         <v>30.8</v>
       </c>
       <c r="O237" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P237" t="n">
         <v>0.9245290682754905</v>
@@ -15680,7 +15680,7 @@
         <v>18.6</v>
       </c>
       <c r="O238" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P238" t="n">
         <v>-1.185733188093377</v>
@@ -15744,7 +15744,7 @@
         <v>25.5</v>
       </c>
       <c r="O239" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P239" t="n">
         <v>-0.6077571714229204</v>
@@ -16128,7 +16128,7 @@
         <v>35.2</v>
       </c>
       <c r="O245" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P245" t="n">
         <v>1.471314899904323</v>
@@ -16192,7 +16192,7 @@
         <v>22.5</v>
       </c>
       <c r="O246" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P246" t="n">
         <v>-0.2397677075546296</v>
@@ -16256,7 +16256,7 @@
         <v>30.8</v>
       </c>
       <c r="O247" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P247" t="n">
         <v>0.9245290682754905</v>
@@ -16320,7 +16320,7 @@
         <v>18.6</v>
       </c>
       <c r="O248" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P248" t="n">
         <v>-1.185733188093377</v>
@@ -16384,7 +16384,7 @@
         <v>25.5</v>
       </c>
       <c r="O249" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P249" t="n">
         <v>-0.6077571714229204</v>
@@ -16768,7 +16768,7 @@
         <v>35.2</v>
       </c>
       <c r="O255" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P255" t="n">
         <v>1.471314899904323</v>
@@ -16832,7 +16832,7 @@
         <v>22.5</v>
       </c>
       <c r="O256" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P256" t="n">
         <v>-0.2397677075546296</v>
@@ -16896,7 +16896,7 @@
         <v>30.8</v>
       </c>
       <c r="O257" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P257" t="n">
         <v>0.9245290682754905</v>
@@ -16960,7 +16960,7 @@
         <v>18.6</v>
       </c>
       <c r="O258" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P258" t="n">
         <v>-1.185733188093377</v>
@@ -17024,7 +17024,7 @@
         <v>25.5</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P259" t="n">
         <v>-0.6077571714229204</v>
@@ -17408,7 +17408,7 @@
         <v>35.2</v>
       </c>
       <c r="O265" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P265" t="n">
         <v>1.471314899904323</v>
@@ -17472,7 +17472,7 @@
         <v>22.5</v>
       </c>
       <c r="O266" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P266" t="n">
         <v>-0.2397677075546296</v>
@@ -17536,7 +17536,7 @@
         <v>30.8</v>
       </c>
       <c r="O267" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P267" t="n">
         <v>0.9245290682754905</v>
@@ -17600,7 +17600,7 @@
         <v>18.6</v>
       </c>
       <c r="O268" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P268" t="n">
         <v>-1.185733188093377</v>
@@ -17664,7 +17664,7 @@
         <v>25.5</v>
       </c>
       <c r="O269" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P269" t="n">
         <v>-0.6077571714229204</v>
@@ -18048,7 +18048,7 @@
         <v>35.2</v>
       </c>
       <c r="O275" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P275" t="n">
         <v>1.471314899904323</v>
@@ -18112,7 +18112,7 @@
         <v>22.5</v>
       </c>
       <c r="O276" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P276" t="n">
         <v>-0.2397677075546296</v>
@@ -18176,7 +18176,7 @@
         <v>30.8</v>
       </c>
       <c r="O277" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P277" t="n">
         <v>0.9245290682754905</v>
@@ -18240,7 +18240,7 @@
         <v>18.6</v>
       </c>
       <c r="O278" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P278" t="n">
         <v>-1.185733188093377</v>
@@ -18304,7 +18304,7 @@
         <v>25.5</v>
       </c>
       <c r="O279" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P279" t="n">
         <v>-0.6077571714229204</v>
@@ -18688,7 +18688,7 @@
         <v>35.2</v>
       </c>
       <c r="O285" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P285" t="n">
         <v>1.471314899904323</v>
@@ -18752,7 +18752,7 @@
         <v>22.5</v>
       </c>
       <c r="O286" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P286" t="n">
         <v>-0.2397677075546296</v>
@@ -18816,7 +18816,7 @@
         <v>30.8</v>
       </c>
       <c r="O287" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P287" t="n">
         <v>0.9245290682754905</v>
@@ -18880,7 +18880,7 @@
         <v>18.6</v>
       </c>
       <c r="O288" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P288" t="n">
         <v>-1.185733188093377</v>
@@ -18944,7 +18944,7 @@
         <v>25.5</v>
       </c>
       <c r="O289" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P289" t="n">
         <v>-0.6077571714229204</v>
@@ -19328,7 +19328,7 @@
         <v>35.2</v>
       </c>
       <c r="O295" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P295" t="n">
         <v>1.471314899904323</v>
@@ -19392,7 +19392,7 @@
         <v>22.5</v>
       </c>
       <c r="O296" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P296" t="n">
         <v>-0.2397677075546296</v>
@@ -19456,7 +19456,7 @@
         <v>30.8</v>
       </c>
       <c r="O297" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P297" t="n">
         <v>0.9245290682754905</v>
@@ -19520,7 +19520,7 @@
         <v>18.6</v>
       </c>
       <c r="O298" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P298" t="n">
         <v>-1.185733188093377</v>
@@ -19584,7 +19584,7 @@
         <v>25.5</v>
       </c>
       <c r="O299" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P299" t="n">
         <v>-0.6077571714229204</v>
@@ -19968,7 +19968,7 @@
         <v>35.2</v>
       </c>
       <c r="O305" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P305" t="n">
         <v>1.471314899904323</v>
@@ -20032,7 +20032,7 @@
         <v>22.5</v>
       </c>
       <c r="O306" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P306" t="n">
         <v>-0.2397677075546296</v>
@@ -20096,7 +20096,7 @@
         <v>30.8</v>
       </c>
       <c r="O307" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P307" t="n">
         <v>0.9245290682754905</v>
@@ -20160,7 +20160,7 @@
         <v>18.6</v>
       </c>
       <c r="O308" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P308" t="n">
         <v>-1.185733188093377</v>
@@ -20224,7 +20224,7 @@
         <v>25.5</v>
       </c>
       <c r="O309" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P309" t="n">
         <v>-0.6077571714229204</v>
@@ -20608,7 +20608,7 @@
         <v>35.2</v>
       </c>
       <c r="O315" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P315" t="n">
         <v>1.471314899904323</v>
@@ -20672,7 +20672,7 @@
         <v>22.5</v>
       </c>
       <c r="O316" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P316" t="n">
         <v>-0.2397677075546296</v>
@@ -20736,7 +20736,7 @@
         <v>30.8</v>
       </c>
       <c r="O317" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P317" t="n">
         <v>0.9245290682754905</v>
@@ -20800,7 +20800,7 @@
         <v>18.6</v>
       </c>
       <c r="O318" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P318" t="n">
         <v>-1.185733188093377</v>
@@ -20864,7 +20864,7 @@
         <v>25.5</v>
       </c>
       <c r="O319" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P319" t="n">
         <v>-0.6077571714229204</v>
@@ -21248,7 +21248,7 @@
         <v>35.2</v>
       </c>
       <c r="O325" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P325" t="n">
         <v>1.471314899904323</v>
@@ -21312,7 +21312,7 @@
         <v>22.5</v>
       </c>
       <c r="O326" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P326" t="n">
         <v>-0.2397677075546296</v>
@@ -21376,7 +21376,7 @@
         <v>30.8</v>
       </c>
       <c r="O327" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P327" t="n">
         <v>0.9245290682754905</v>
@@ -21440,7 +21440,7 @@
         <v>18.6</v>
       </c>
       <c r="O328" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P328" t="n">
         <v>-1.185733188093377</v>
@@ -21504,7 +21504,7 @@
         <v>25.5</v>
       </c>
       <c r="O329" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P329" t="n">
         <v>-0.6077571714229204</v>
@@ -21888,7 +21888,7 @@
         <v>35.2</v>
       </c>
       <c r="O335" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P335" t="n">
         <v>1.471314899904323</v>
@@ -21952,7 +21952,7 @@
         <v>22.5</v>
       </c>
       <c r="O336" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P336" t="n">
         <v>-0.2397677075546296</v>
@@ -22016,7 +22016,7 @@
         <v>30.8</v>
       </c>
       <c r="O337" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P337" t="n">
         <v>0.9245290682754905</v>
@@ -22080,7 +22080,7 @@
         <v>18.6</v>
       </c>
       <c r="O338" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P338" t="n">
         <v>-1.185733188093377</v>
@@ -22144,7 +22144,7 @@
         <v>25.5</v>
       </c>
       <c r="O339" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P339" t="n">
         <v>-0.6077571714229204</v>
@@ -22528,7 +22528,7 @@
         <v>35.2</v>
       </c>
       <c r="O345" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P345" t="n">
         <v>1.471314899904323</v>
@@ -22592,7 +22592,7 @@
         <v>22.5</v>
       </c>
       <c r="O346" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P346" t="n">
         <v>-0.2397677075546296</v>
@@ -22656,7 +22656,7 @@
         <v>30.8</v>
       </c>
       <c r="O347" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P347" t="n">
         <v>0.9245290682754905</v>
@@ -22720,7 +22720,7 @@
         <v>18.6</v>
       </c>
       <c r="O348" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P348" t="n">
         <v>-1.185733188093377</v>
@@ -22784,7 +22784,7 @@
         <v>25.5</v>
       </c>
       <c r="O349" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P349" t="n">
         <v>-0.6077571714229204</v>
@@ -23168,7 +23168,7 @@
         <v>35.2</v>
       </c>
       <c r="O355" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P355" t="n">
         <v>1.471314899904323</v>
@@ -23232,7 +23232,7 @@
         <v>22.5</v>
       </c>
       <c r="O356" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P356" t="n">
         <v>-0.2397677075546296</v>
@@ -23296,7 +23296,7 @@
         <v>30.8</v>
       </c>
       <c r="O357" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P357" t="n">
         <v>0.9245290682754905</v>
@@ -23360,7 +23360,7 @@
         <v>18.6</v>
       </c>
       <c r="O358" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P358" t="n">
         <v>-1.185733188093377</v>
@@ -23424,7 +23424,7 @@
         <v>25.5</v>
       </c>
       <c r="O359" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P359" t="n">
         <v>-0.6077571714229204</v>
@@ -23808,7 +23808,7 @@
         <v>35.2</v>
       </c>
       <c r="O365" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P365" t="n">
         <v>1.471314899904323</v>
@@ -23872,7 +23872,7 @@
         <v>22.5</v>
       </c>
       <c r="O366" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P366" t="n">
         <v>-0.2397677075546296</v>
@@ -23936,7 +23936,7 @@
         <v>30.8</v>
       </c>
       <c r="O367" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P367" t="n">
         <v>0.9245290682754905</v>
@@ -24000,7 +24000,7 @@
         <v>18.6</v>
       </c>
       <c r="O368" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P368" t="n">
         <v>-1.185733188093377</v>
@@ -24064,7 +24064,7 @@
         <v>25.5</v>
       </c>
       <c r="O369" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P369" t="n">
         <v>-0.6077571714229204</v>
@@ -24448,7 +24448,7 @@
         <v>35.2</v>
       </c>
       <c r="O375" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P375" t="n">
         <v>1.471314899904323</v>
@@ -24512,7 +24512,7 @@
         <v>22.5</v>
       </c>
       <c r="O376" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P376" t="n">
         <v>-0.2397677075546296</v>
@@ -24576,7 +24576,7 @@
         <v>30.8</v>
       </c>
       <c r="O377" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P377" t="n">
         <v>0.9245290682754905</v>
@@ -24640,7 +24640,7 @@
         <v>18.6</v>
       </c>
       <c r="O378" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P378" t="n">
         <v>-1.185733188093377</v>
@@ -24704,7 +24704,7 @@
         <v>25.5</v>
       </c>
       <c r="O379" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P379" t="n">
         <v>-0.6077571714229204</v>
@@ -25088,7 +25088,7 @@
         <v>35.2</v>
       </c>
       <c r="O385" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P385" t="n">
         <v>1.471314899904323</v>
@@ -25152,7 +25152,7 @@
         <v>22.5</v>
       </c>
       <c r="O386" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P386" t="n">
         <v>-0.2397677075546296</v>
@@ -25216,7 +25216,7 @@
         <v>30.8</v>
       </c>
       <c r="O387" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P387" t="n">
         <v>0.9245290682754905</v>
@@ -25280,7 +25280,7 @@
         <v>18.6</v>
       </c>
       <c r="O388" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P388" t="n">
         <v>-1.185733188093377</v>
@@ -25344,7 +25344,7 @@
         <v>25.5</v>
       </c>
       <c r="O389" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P389" t="n">
         <v>-0.6077571714229204</v>
@@ -25728,7 +25728,7 @@
         <v>35.2</v>
       </c>
       <c r="O395" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P395" t="n">
         <v>1.471314899904323</v>
@@ -25792,7 +25792,7 @@
         <v>22.5</v>
       </c>
       <c r="O396" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P396" t="n">
         <v>-0.2397677075546296</v>
@@ -25856,7 +25856,7 @@
         <v>30.8</v>
       </c>
       <c r="O397" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P397" t="n">
         <v>0.9245290682754905</v>
@@ -25920,7 +25920,7 @@
         <v>18.6</v>
       </c>
       <c r="O398" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P398" t="n">
         <v>-1.185733188093377</v>
@@ -25984,7 +25984,7 @@
         <v>25.5</v>
       </c>
       <c r="O399" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P399" t="n">
         <v>-0.6077571714229204</v>
@@ -26368,7 +26368,7 @@
         <v>35.2</v>
       </c>
       <c r="O405" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P405" t="n">
         <v>1.471314899904323</v>
@@ -26432,7 +26432,7 @@
         <v>22.5</v>
       </c>
       <c r="O406" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P406" t="n">
         <v>-0.2397677075546296</v>
@@ -26496,7 +26496,7 @@
         <v>30.8</v>
       </c>
       <c r="O407" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P407" t="n">
         <v>0.9245290682754905</v>
@@ -26560,7 +26560,7 @@
         <v>18.6</v>
       </c>
       <c r="O408" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P408" t="n">
         <v>-1.185733188093377</v>
@@ -26624,7 +26624,7 @@
         <v>25.5</v>
       </c>
       <c r="O409" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P409" t="n">
         <v>-0.6077571714229204</v>
@@ -27008,7 +27008,7 @@
         <v>35.2</v>
       </c>
       <c r="O415" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P415" t="n">
         <v>1.471314899904323</v>
@@ -27072,7 +27072,7 @@
         <v>22.5</v>
       </c>
       <c r="O416" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P416" t="n">
         <v>-0.2397677075546296</v>
@@ -27136,7 +27136,7 @@
         <v>30.8</v>
       </c>
       <c r="O417" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P417" t="n">
         <v>0.9245290682754905</v>
@@ -27200,7 +27200,7 @@
         <v>18.6</v>
       </c>
       <c r="O418" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P418" t="n">
         <v>-1.185733188093377</v>
@@ -27264,7 +27264,7 @@
         <v>25.5</v>
       </c>
       <c r="O419" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P419" t="n">
         <v>-0.6077571714229204</v>
@@ -27648,7 +27648,7 @@
         <v>35.2</v>
       </c>
       <c r="O425" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P425" t="n">
         <v>1.471314899904323</v>
@@ -27712,7 +27712,7 @@
         <v>22.5</v>
       </c>
       <c r="O426" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P426" t="n">
         <v>-0.2397677075546296</v>
@@ -27776,7 +27776,7 @@
         <v>30.8</v>
       </c>
       <c r="O427" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P427" t="n">
         <v>0.9245290682754905</v>
@@ -27840,7 +27840,7 @@
         <v>18.6</v>
       </c>
       <c r="O428" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P428" t="n">
         <v>-1.185733188093377</v>
@@ -27904,7 +27904,7 @@
         <v>25.5</v>
       </c>
       <c r="O429" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P429" t="n">
         <v>-0.6077571714229204</v>
@@ -28288,7 +28288,7 @@
         <v>35.2</v>
       </c>
       <c r="O435" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P435" t="n">
         <v>1.471314899904323</v>
@@ -28352,7 +28352,7 @@
         <v>22.5</v>
       </c>
       <c r="O436" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P436" t="n">
         <v>-0.2397677075546296</v>
@@ -28416,7 +28416,7 @@
         <v>30.8</v>
       </c>
       <c r="O437" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P437" t="n">
         <v>0.9245290682754905</v>
@@ -28480,7 +28480,7 @@
         <v>18.6</v>
       </c>
       <c r="O438" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P438" t="n">
         <v>-1.185733188093377</v>
@@ -28544,7 +28544,7 @@
         <v>25.5</v>
       </c>
       <c r="O439" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P439" t="n">
         <v>-0.6077571714229204</v>
@@ -28928,7 +28928,7 @@
         <v>35.2</v>
       </c>
       <c r="O445" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P445" t="n">
         <v>1.471314899904323</v>
@@ -28992,7 +28992,7 @@
         <v>22.5</v>
       </c>
       <c r="O446" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P446" t="n">
         <v>-0.2397677075546296</v>
@@ -29056,7 +29056,7 @@
         <v>30.8</v>
       </c>
       <c r="O447" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P447" t="n">
         <v>0.9245290682754905</v>
@@ -29120,7 +29120,7 @@
         <v>18.6</v>
       </c>
       <c r="O448" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P448" t="n">
         <v>-1.185733188093377</v>
@@ -29184,7 +29184,7 @@
         <v>25.5</v>
       </c>
       <c r="O449" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P449" t="n">
         <v>-0.6077571714229204</v>
@@ -29568,7 +29568,7 @@
         <v>35.2</v>
       </c>
       <c r="O455" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P455" t="n">
         <v>1.471314899904323</v>
@@ -29632,7 +29632,7 @@
         <v>22.5</v>
       </c>
       <c r="O456" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P456" t="n">
         <v>-0.2397677075546296</v>
@@ -29696,7 +29696,7 @@
         <v>30.8</v>
       </c>
       <c r="O457" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P457" t="n">
         <v>0.9245290682754905</v>
@@ -29760,7 +29760,7 @@
         <v>18.6</v>
       </c>
       <c r="O458" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P458" t="n">
         <v>-1.185733188093377</v>
@@ -29824,7 +29824,7 @@
         <v>25.5</v>
       </c>
       <c r="O459" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P459" t="n">
         <v>-0.6077571714229204</v>
@@ -30208,7 +30208,7 @@
         <v>35.2</v>
       </c>
       <c r="O465" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P465" t="n">
         <v>1.471314899904323</v>
@@ -30272,7 +30272,7 @@
         <v>22.5</v>
       </c>
       <c r="O466" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P466" t="n">
         <v>-0.2397677075546296</v>
@@ -30336,7 +30336,7 @@
         <v>30.8</v>
       </c>
       <c r="O467" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P467" t="n">
         <v>0.9245290682754905</v>
@@ -30400,7 +30400,7 @@
         <v>18.6</v>
       </c>
       <c r="O468" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P468" t="n">
         <v>-1.185733188093377</v>
@@ -30464,7 +30464,7 @@
         <v>25.5</v>
       </c>
       <c r="O469" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P469" t="n">
         <v>-0.6077571714229204</v>
@@ -30848,7 +30848,7 @@
         <v>35.2</v>
       </c>
       <c r="O475" t="n">
-        <v>0.5561460189861002</v>
+        <v>0.5561460189861003</v>
       </c>
       <c r="P475" t="n">
         <v>1.471314899904323</v>
@@ -30912,7 +30912,7 @@
         <v>22.5</v>
       </c>
       <c r="O476" t="n">
-        <v>-0.08741981179671728</v>
+        <v>-0.08741981179671729</v>
       </c>
       <c r="P476" t="n">
         <v>-0.2397677075546296</v>
@@ -30976,7 +30976,7 @@
         <v>30.8</v>
       </c>
       <c r="O477" t="n">
-        <v>-0.3663831297513245</v>
+        <v>-0.3663831297513246</v>
       </c>
       <c r="P477" t="n">
         <v>0.9245290682754905</v>
@@ -31040,7 +31040,7 @@
         <v>18.6</v>
       </c>
       <c r="O478" t="n">
-        <v>-0.9675533195076059</v>
+        <v>-0.967553319507606</v>
       </c>
       <c r="P478" t="n">
         <v>-1.185733188093377</v>
@@ -31104,7 +31104,7 @@
         <v>25.5</v>
       </c>
       <c r="O479" t="n">
-        <v>-0.9098952477115169</v>
+        <v>-0.909895247711517</v>
       </c>
       <c r="P479" t="n">
         <v>-0.6077571714229204</v>
